--- a/data/chandan_jobs.xlsx
+++ b/data/chandan_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>db25ee799a3a06f31bae</t>
+          <t>93b6db8b0a77bfc98ace</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=TmYJrKWn8RGxWp4A46G3QA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=etjpr7Sn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a5aec49a048da1163cb4</t>
+          <t>63c57ead4820210f71f4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427597?se=TmYJrKWn8RGxWp4A46G3QA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=4105AD46275610953DB7E2FEC84FA7A8812D1A99</t>
+          <t>https://www.adzuna.in/land/ad/5864427597?se=etjpr7Sn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=4105AD46275610953DB7E2FEC84FA7A8812D1A99</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21fb1fa5c16cffb86bc6</t>
+          <t>d56ef8dcffd17df567ee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Right Advisors</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Job Description: Proficiency with python and the python ML tool kit along with DL frameworks Experience with working on end to end solutions and comfortable with cloud based ML-Ops pipelines Experience fine-tuning deep learning models including LLMs Experience with GPUs and understanding of balancin</t>
+          <t>Roles &amp; responsibilities : Delivery of Key Projects: Successfully deliver advanced analytics and data science projects within predefined timelines and budget constraints. Collaboration: Collaborate effectively with data engineers and ML engineers to comprehend data and models, utilizing various adva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5807451743?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=bC2JsLSn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52255342784504fa8bcd</t>
+          <t>235b47d5115c81a32be1</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Deep Learning</t>
+          <t>skill:Python, skill:Data Structures</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -922,17 +922,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d518170ec94c48125676</t>
+          <t>8267095de681c8cea699</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Python ML Engineer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Roles &amp; responsibilities : Delivery of Key Projects: Successfully deliver advanced analytics and data science projects within predefined timelines and budget constraints. Collaboration: Collaborate effectively with data engineers and ML engineers to comprehend data and models, utilizing various adva</t>
+          <t>Job Description: We are looking for a Python ML Engineer with strong expertise in Generative AI and Azure Databricks to design build and deploy scalable AI solutions The ideal candidate should have hands on experience with LLMs RAG pipelines and Azure based AI ecosystems along with a solid foundatio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=HiOGrKWn8RGxWp4A46G3QA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/details/5853198518?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>235b47d5115c81a32be1</t>
+          <t>83b3f6e8deeba01c2d75</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Data Structures</t>
+          <t>skill:Python, skill:RAG</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8267095de681c8cea699</t>
+          <t>8ea05990f9754e320d09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Multi Recruit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Python ML Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Job Description: We are looking for a Python ML Engineer with strong expertise in Generative AI and Azure Databricks to design build and deploy scalable AI solutions The ideal candidate should have hands on experience with LLMs RAG pipelines and Azure based AI ecosystems along with a solid foundatio</t>
+          <t>Computer Science fundamentals in object-oriented design, design patterns, data structures, algorithm design, Proficiency with Java 1 years of experience contributing to architecture and design in a product setup Key Responsibilities Understand customer needs by collaborating with Product Managers an</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5853198518?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2171039159?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>83b3f6e8deeba01c2d75</t>
+          <t>e4ec4857e5f35fa49afb</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>skill:Python, skill:RAG</t>
+          <t>skill:Java, skill:Data Structures</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8ea05990f9754e320d09</t>
+          <t>565e04fd2b406ecb5ad5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Computer Science fundamentals in object-oriented design, design patterns, data structures, algorithm design, Proficiency with Java 1 years of experience contributing to architecture and design in a product setup Key Responsibilities Understand customer needs by collaborating with Product Managers an</t>
+          <t>Bachelor's degree in Computer Science (BE/ B.Tech) Strong computer science fundamentals in algorithms, data structures, storage technologies, distributed computing, operating systems, etc. Experience in designing and implementing scalable solutions in a large scale distributed environment. Robust an</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2171039159?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2853928132?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>e4ec4857e5f35fa49afb</t>
+          <t>a93dbd277d84ed26d792</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>skill:Java, skill:Data Structures</t>
+          <t>skill:Java, skill:Data Structures, skill:Algorithms</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1135,17 +1135,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>565e04fd2b406ecb5ad5</t>
+          <t>b625a406d8d76e189728</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Multi Recruit</t>
+          <t>Success Pact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>SDE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bachelor's degree in Computer Science (BE/ B.Tech) Strong computer science fundamentals in algorithms, data structures, storage technologies, distributed computing, operating systems, etc. Experience in designing and implementing scalable solutions in a large scale distributed environment. Robust an</t>
+          <t>Hi, Good exp in data structures, Java, algorithms, and in design, design patterns. Exp-2-8yrs Location- Bangalore, hyderabad, pune, gurgaon. Regards sanchita Skills:- Data Structures, Algorithms, Design patterns and Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2853928132?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/1517699787?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>a93dbd277d84ed26d792</t>
+          <t>4cba866bcbd6995043c8</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1206,17 +1206,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b625a406d8d76e189728</t>
+          <t>bedebd0e647137fbab9e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Success Pact</t>
+          <t>Zorba Consulting India</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SDE</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hi, Good exp in data structures, Java, algorithms, and in design, design patterns. Exp-2-8yrs Location- Bangalore, hyderabad, pune, gurgaon. Regards sanchita Skills:- Data Structures, Algorithms, Design patterns and Java</t>
+          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/1517699787?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1246,20 +1246,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4cba866bcbd6995043c8</t>
+          <t>443a693318c3c6f3b107</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>skill:Java, skill:Data Structures, skill:Algorithms</t>
+          <t>skill:Python, skill:SQL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>78723e7ad5a8abc08a88</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Conneqt Business Solutions Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1317,20 +1317,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>72e4255119e60b04397d</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL</t>
+          <t>skill:Python, skill:SQL, skill:Redis</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1348,17 +1348,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>78723e7ad5a8abc08a88</t>
+          <t>7eedeb2d5606cf5134d1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Conneqt Business Solutions Limited</t>
+          <t>Mobile Programming India Pvt Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+          <t>Proven hands-on Software Development experience Proven working experience in Java development Hands on experience in designing and developing applications using Java EE platforms Object Oriented analysis and design using common design patterns. Profound insight of Java and JEE internals (Classloadin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2605401465?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>72e4255119e60b04397d</t>
+          <t>ef70681f7ea5dee65dfc</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL, skill:Redis</t>
+          <t>skill:Java, skill:SQL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1419,52 +1419,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7eedeb2d5606cf5134d1</t>
+          <t>80fe07aa997dd3123a30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mobile Programming India Pvt Ltd</t>
+          <t>Gramian Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Proven hands-on Software Development experience Proven working experience in Java development Hands on experience in designing and developing applications using Java EE platforms Object Oriented analysis and design using common design patterns. Profound insight of Java and JEE internals (Classloadin</t>
+          <t>&amp;nbsp;...supporting the development of advanced AI systems by incorporating high-quality software &lt;b&gt;engineering &lt;/b&gt;expertise into training and evaluation workflows.  We are looking for experienced  Java &lt;b&gt;backend &lt;/b&gt;engineers  with strong hands-on expertise in  Spring Boot, microservices, REST..</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2605401465?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=298&amp;brelb=15&amp;scr=115.879395&amp;bscr=115.879395&amp;aq=9168212927939098093&amp;elckey=4792597070204193617</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>jooble</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ef70681f7ea5dee65dfc</t>
+          <t>8f12ed9dd8f7b3e366e9</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>skill:Java, skill:SQL</t>
+          <t>skill:Java, skill:Spring Boot</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1490,17 +1490,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>c4ad4ef16308c48c1284</t>
+          <t>918ef1581a1d65fd1443</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gramian Consulting</t>
+          <t>Merkle Science</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1509,77 +1509,6 @@
         </is>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...supporting the development of advanced AI systems by incorporating high-quality software &lt;b&gt;engineering &lt;/b&gt;expertise into training and evaluation workflows.  We are looking for experienced  Java &lt;b&gt;backend &lt;/b&gt;engineers  with strong hands-on expertise in  Spring Boot, microservices, REST..</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=296&amp;brelb=15&amp;scr=117.14296&amp;bscr=117.14296&amp;aq=-8218117139647685250&amp;elckey=-5712181725608664146</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>8f12ed9dd8f7b3e366e9</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>20</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:Spring Boot</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3f0315c07e22411c570b</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Merkle Science</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Software Engineer(Intern)- Backend</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>&amp;nbsp;...several others. 
  Responsibilities 
@@ -1589,82 +1518,156 @@
  Write clean, tested, well-d</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-5712181725608664146&amp;p=1&amp;aq=-8218117139647685250&amp;cid=18943&amp;jobAge=656&amp;brelb=15&amp;bscr=57.430958&amp;scr=57.430958</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=9168212927939098093&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.83042&amp;scr=56.83042</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>68457383d022598649bc</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K16" t="n">
         <v>20</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5beb9baa57d4adfcc2b9</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7eccc9ed1647c4ec7157</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Sophos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Full Stack Software Engineer</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>&amp;nbsp;...development of next-generation web applications, UI frameworks, and &lt;b&gt;developer &lt;/b&gt;platforms. The ideal candidate should have strong experience in...&amp;nbsp;&amp;nbsp;.... 
  Strong development experience in  Java  ,  Go  , or  &lt;b&gt;Python &lt;/b&gt; . 
  Experience building  RESTful APIs  ,  microserv</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-796507398843211532?p=1&amp;pos=2&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=898&amp;brelb=15&amp;scr=52.591484&amp;bscr=52.591484&amp;aq=5601475440488524&amp;elckey=-411309993333774135</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5537fa1f7e5e07c1c9a1</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Java</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ebb6a414971bb98a4803</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SaidGig</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, India</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...contribute working code early. 
+ Key Responsibilities 
+ Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
+ Integrate pre-release model APIs into functional...&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=7530655284562919718&amp;p=1&amp;aq=-6175106300378282697&amp;cid=18943&amp;jobAge=896&amp;brelb=15&amp;bscr=53.270027&amp;scr=53.270027</t>
+          <t>https://jooble.org/desc/-4293671604513188386?ckey=Python+Developer&amp;rgn=55126&amp;pos=4&amp;groupId=40830&amp;elckey=-411309993333774135&amp;p=1&amp;aq=5601475440488524&amp;cid=18943&amp;jobAge=562&amp;brelb=15&amp;bscr=52.418476&amp;scr=52.418476</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1674,17 +1677,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5537fa1f7e5e07c1c9a1</t>
+          <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1710,7 +1713,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e1b422afc0b7928deb8f</t>
+          <t>37bd788baabe5864667e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1739,7 +1742,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=4&amp;groupId=40830&amp;elckey=7530655284562919718&amp;p=1&amp;aq=-6175106300378282697&amp;cid=18943&amp;jobAge=656&amp;brelb=15&amp;bscr=52.80803&amp;scr=52.80803</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=658&amp;brelb=15&amp;scr=52.026104&amp;bscr=52.026104&amp;aq=5601475440488524&amp;elckey=-411309993333774135</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1749,12 +1752,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-03 16:31:02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1785,17 +1788,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09dbde6fc95fe8da969d</t>
+          <t>8e4f050732a59d934b5f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SaidGig</t>
+          <t>Gramian Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, India</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1804,80 +1807,6 @@
         </is>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...contribute working code early. 
- Key Responsibilities 
- Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
- Integrate pre-release model APIs into functional...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=560&amp;brelb=15&amp;scr=52.80085&amp;bscr=52.80085&amp;aq=-6175106300378282697&amp;elckey=7530655284562919718</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>4a9ec70bde1620a4856a</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>20</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:Java</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1ab473630d540ad7fc70</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Gramian Consulting</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Java Backend Engineer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>&amp;nbsp;...software outputs that help train next-generation AI systems.  No prior AI experience is required  . 
  Responsibilities 
@@ -1886,50 +1815,50 @@
  Architect and implement...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=296&amp;brelb=15&amp;scr=51.74756&amp;bscr=51.74756&amp;aq=-6175106300378282697&amp;elckey=7530655284562919718</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2667151008715974299?ckey=Python+Developer&amp;rgn=55126&amp;pos=8&amp;groupId=40830&amp;elckey=-411309993333774135&amp;p=1&amp;aq=5601475440488524&amp;cid=18943&amp;jobAge=298&amp;brelb=15&amp;bscr=51.011112&amp;scr=51.011112</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:43:21</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:31:02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>10fcce4d8693e6d01c32</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K20" t="n">
         <v>20</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>skill:Java, skill:Spring Boot</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/chandan_jobs.xlsx
+++ b/data/chandan_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>93b6db8b0a77bfc98ace</t>
+          <t>581d95f9a84ec6ad5073</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=etjpr7Sn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=es7EOgio8RGq2pU5YSNUPA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63c57ead4820210f71f4</t>
+          <t>64623d53b689b407c247</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427597?se=etjpr7Sn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=4105AD46275610953DB7E2FEC84FA7A8812D1A99</t>
+          <t>https://www.adzuna.in/land/ad/5864427597?se=es7EOgio8RGq2pU5YSNUPA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=4105AD46275610953DB7E2FEC84FA7A8812D1A99</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d56ef8dcffd17df567ee</t>
+          <t>38feb92b14203afb4bdd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=bC2JsLSn8RGgftATrmZl1Q&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=Zu9DOwio8RGFQ8r7cmJIsQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1206,12 +1206,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>78723e7ad5a8abc08a88</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Conneqt Business Solutions Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1246,20 +1246,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>72e4255119e60b04397d</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL</t>
+          <t>skill:Python, skill:SQL, skill:Redis</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>78723e7ad5a8abc08a88</t>
+          <t>7eedeb2d5606cf5134d1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Conneqt Business Solutions Limited</t>
+          <t>Mobile Programming India Pvt Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+          <t>Proven hands-on Software Development experience Proven working experience in Java development Hands on experience in designing and developing applications using Java EE platforms Object Oriented analysis and design using common design patterns. Profound insight of Java and JEE internals (Classloadin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2605401465?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1317,20 +1317,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>72e4255119e60b04397d</t>
+          <t>ef70681f7ea5dee65dfc</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL, skill:Redis</t>
+          <t>skill:Java, skill:SQL</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1348,52 +1348,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7eedeb2d5606cf5134d1</t>
+          <t>39643b715981382fd013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Programming India Pvt Ltd</t>
+          <t>Gramian Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Proven hands-on Software Development experience Proven working experience in Java development Hands on experience in designing and developing applications using Java EE platforms Object Oriented analysis and design using common design patterns. Profound insight of Java and JEE internals (Classloadin</t>
+          <t>&amp;nbsp;...supporting the development of advanced AI systems by incorporating high-quality software &lt;b&gt;engineering &lt;/b&gt;expertise into training and evaluation workflows.  We are looking for experienced  Java &lt;b&gt;backend &lt;/b&gt;engineers  with strong hands-on expertise in  Spring Boot, microservices, REST..</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2605401465?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://jooble.org/desc/-2667151008715974299?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=4&amp;groupId=41745&amp;elckey=-7487284121957792138&amp;p=1&amp;aq=-8670933589022086134&amp;cid=18943&amp;jobAge=308&amp;brelb=15&amp;bscr=116.634026&amp;scr=116.634026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>jooble</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:21</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:02</t>
+          <t>2026-09-04 02:28:48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ef70681f7ea5dee65dfc</t>
+          <t>8f12ed9dd8f7b3e366e9</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>skill:Java, skill:SQL</t>
+          <t>skill:Java, skill:Spring Boot</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1419,17 +1419,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>80fe07aa997dd3123a30</t>
+          <t>e477ac4e12b13ac1a884</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gramian Consulting</t>
+          <t>Merkle Science</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1438,77 +1438,6 @@
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...supporting the development of advanced AI systems by incorporating high-quality software &lt;b&gt;engineering &lt;/b&gt;expertise into training and evaluation workflows.  We are looking for experienced  Java &lt;b&gt;backend &lt;/b&gt;engineers  with strong hands-on expertise in  Spring Boot, microservices, REST..</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=298&amp;brelb=15&amp;scr=115.879395&amp;bscr=115.879395&amp;aq=9168212927939098093&amp;elckey=4792597070204193617</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>8f12ed9dd8f7b3e366e9</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:Spring Boot</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>918ef1581a1d65fd1443</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Merkle Science</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Software Engineer(Intern)- Backend</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>&amp;nbsp;...several others. 
  Responsibilities 
@@ -1518,146 +1447,146 @@
  Write clean, tested, well-d</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=9168212927939098093&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.83042&amp;scr=56.83042</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-7487284121957792138&amp;p=1&amp;aq=-8670933589022086134&amp;cid=18943&amp;jobAge=668&amp;brelb=15&amp;bscr=57.15673&amp;scr=57.15673</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>68457383d022598649bc</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K15" t="n">
         <v>20</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7eccc9ed1647c4ec7157</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0a424e18cb5e814b51bd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Sophos</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Full Stack Software Engineer</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>&amp;nbsp;...development of next-generation web applications, UI frameworks, and &lt;b&gt;developer &lt;/b&gt;platforms. The ideal candidate should have strong experience in...&amp;nbsp;&amp;nbsp;.... 
  Strong development experience in  Java  ,  Go  , or  &lt;b&gt;Python &lt;/b&gt; . 
  Experience building  RESTful APIs  ,  microserv</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-796507398843211532?p=1&amp;pos=2&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=898&amp;brelb=15&amp;scr=52.591484&amp;bscr=52.591484&amp;aq=5601475440488524&amp;elckey=-411309993333774135</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-796507398843211532?p=1&amp;pos=2&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=908&amp;brelb=15&amp;scr=53.25766&amp;bscr=53.25766&amp;aq=-392041409776048339&amp;elckey=5755552888213791726</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>5537fa1f7e5e07c1c9a1</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K16" t="n">
         <v>20</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>skill:Python, skill:Java</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ebb6a414971bb98a4803</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>653956cdde969f996557</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>SaidGig</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer, India</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>&amp;nbsp;...contribute working code early. 
  Key Responsibilities 
@@ -1665,73 +1594,73 @@
  Integrate pre-release model APIs into functional...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-4293671604513188386?ckey=Python+Developer&amp;rgn=55126&amp;pos=4&amp;groupId=40830&amp;elckey=-411309993333774135&amp;p=1&amp;aq=5601475440488524&amp;cid=18943&amp;jobAge=562&amp;brelb=15&amp;bscr=52.418476&amp;scr=52.418476</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=572&amp;brelb=15&amp;scr=52.713013&amp;bscr=52.713013&amp;aq=-392041409776048339&amp;elckey=5755552888213791726</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K17" t="n">
         <v>20</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>skill:Python, skill:Java</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>37bd788baabe5864667e</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4162c48d3bb7e495903c</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -1740,73 +1669,73 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=658&amp;brelb=15&amp;scr=52.026104&amp;bscr=52.026104&amp;aq=5601475440488524&amp;elckey=-411309993333774135</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=5755552888213791726&amp;p=1&amp;aq=-392041409776048339&amp;cid=18943&amp;jobAge=668&amp;brelb=15&amp;bscr=52.409454&amp;scr=52.409454</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>c88e76ee05d5f22f3af4</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K18" t="n">
         <v>30</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>skill:Python, skill:REST APIs, skill:Redis</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>8e4f050732a59d934b5f</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>80497e0fd3c5a4636a38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Gramian Consulting</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Java Backend Engineer</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>&amp;nbsp;...software outputs that help train next-generation AI systems.  No prior AI experience is required  . 
  Responsibilities 
@@ -1815,50 +1744,50 @@
  Architect and implement...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-2667151008715974299?ckey=Python+Developer&amp;rgn=55126&amp;pos=8&amp;groupId=40830&amp;elckey=-411309993333774135&amp;p=1&amp;aq=5601475440488524&amp;cid=18943&amp;jobAge=298&amp;brelb=15&amp;bscr=51.011112&amp;scr=51.011112</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=308&amp;brelb=15&amp;scr=51.150208&amp;bscr=51.150208&amp;aq=-392041409776048339&amp;elckey=5755552888213791726</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:31:02</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:28:48</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>10fcce4d8693e6d01c32</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K19" t="n">
         <v>20</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>skill:Java, skill:Spring Boot</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/chandan_jobs.xlsx
+++ b/data/chandan_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,77 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>616d0cf16928975fd278</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5876028775?se=YgCE5mWs8RGnuL6Fc8YS3w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:49:40</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:49:40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>61b0829734ac4f5c1943</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Spring Boot</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/chandan_jobs.xlsx
+++ b/data/chandan_jobs.xlsx
@@ -496,60 +496,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>616d0cf16928975fd278</t>
+          <t>b089a3cfab02f278c172</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>capco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
+          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
+&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028775?se=YgCE5mWs8RGnuL6Fc8YS3w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
+          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>arbeitnow</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:49:40</t>
+          <t>2026-09-10 15:44:28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:49:40</t>
+          <t>2026-09-10 15:44:28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61b0829734ac4f5c1943</t>
+          <t>b170f1c2eea6a07ed122</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Java, skill:Spring Boot</t>
+          <t>skill:Java, skill:REST APIs, skill:SQL, skill:Jenkins, skill:CI/CD</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/data/chandan_jobs.xlsx
+++ b/data/chandan_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,74 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>b089a3cfab02f278c172</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>capco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
-&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>arbeitnow</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:44:28</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:44:28</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>b170f1c2eea6a07ed122</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:REST APIs, skill:SQL, skill:Jenkins, skill:CI/CD</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
